--- a/data/trans_dic/IP44C$recibos_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$recibos_2023-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que han tenido, al menos, algún retraso en el pago de recibos</t>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de recibos (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -571,24 +572,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,07</t>
+          <t>0,0; 3,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,79</t>
+          <t>0,0; 1,78</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -621,24 +622,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 6,68</t>
+          <t>0,79; 7,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,68; 9,35</t>
+          <t>2,7; 9,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,44; 7,07</t>
+          <t>2,48; 6,91</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 9,71</t>
+          <t>0,97; 10,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 10,87</t>
+          <t>1,17; 10,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,82; 8,76</t>
+          <t>2,07; 8,88</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,98; 18,16</t>
+          <t>3,79; 16,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,46</t>
+          <t>0,0; 11,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 10,47</t>
+          <t>2,8; 10,58</t>
         </is>
       </c>
     </row>
@@ -771,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,33</t>
+          <t>0,0; 6,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,81</t>
+          <t>0,0; 19,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 12,0</t>
+          <t>0,5; 13,61</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -821,24 +822,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,21; 17,26</t>
+          <t>3,14; 16,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,72; 9,76</t>
+          <t>1,72; 10,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,57; 11,42</t>
+          <t>3,32; 10,74</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,71; 11,42</t>
+          <t>3,75; 11,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,56; 7,77</t>
+          <t>1,56; 8,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,37; 8,12</t>
+          <t>3,37; 8,23</t>
         </is>
       </c>
     </row>
@@ -921,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>19,7; 32,49</t>
+          <t>19,81; 33,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>22,49; 35,72</t>
+          <t>22,3; 35,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22,63; 31,81</t>
+          <t>23,03; 32,6</t>
         </is>
       </c>
     </row>
@@ -971,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,16; 11,0</t>
+          <t>6,98; 10,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,23; 10,96</t>
+          <t>7,24; 10,94</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,54; 10,42</t>
+          <t>7,63; 10,34</t>
         </is>
       </c>
     </row>
@@ -1007,4 +1008,750 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de recibos (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>526</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>526</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2608</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2684</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3851</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6796</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10647</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>995; 9238</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3415; 12168</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>6267; 17450</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2157</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2972</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5128</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>542; 6093</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>770; 7061</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2514; 10801</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>5610</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2367</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7978</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2547; 10763</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 8801</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>3952; 14910</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2264</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2625</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2084</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 7975</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>375; 10173</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>3616</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>6234</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>1430; 7455</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>955; 6067</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>3358; 10861</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>8363</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>5917</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>14280</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>4490; 13840</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2373; 12339</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>9136; 22323</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>33636</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>43340</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>76976</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>25907; 43505</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>33995; 53564</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>65234; 92325</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>58120</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>66273</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>124393</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>45492; 71648</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>53846; 81387</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>106580; 144431</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP44C$recibos_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$recibos_2023-Provincia-trans_dic.xlsx
@@ -572,7 +572,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,59</t>
+          <t>0,0; 3,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,78</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 7,33</t>
+          <t>0,9; 6,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,7; 9,61</t>
+          <t>2,7; 9,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 6,91</t>
+          <t>2,46; 6,83</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 10,91</t>
+          <t>0,96; 10,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 10,74</t>
+          <t>1,15; 11,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 8,88</t>
+          <t>1,82; 8,17</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,79; 16,0</t>
+          <t>3,62; 15,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,95</t>
+          <t>0,0; 10,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,8; 10,58</t>
+          <t>2,51; 10,71</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,04</t>
+          <t>0,0; 5,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,83</t>
+          <t>0,0; 22,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 13,61</t>
+          <t>0,5; 10,71</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,14; 16,39</t>
+          <t>3,07; 16,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,72; 10,91</t>
+          <t>1,94; 9,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,32; 10,74</t>
+          <t>3,36; 10,52</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,75; 11,57</t>
+          <t>3,73; 11,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,56; 8,13</t>
+          <t>1,65; 7,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,37; 8,23</t>
+          <t>3,35; 8,1</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>19,81; 33,27</t>
+          <t>20,02; 32,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>22,3; 35,13</t>
+          <t>21,88; 35,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23,03; 32,6</t>
+          <t>22,39; 31,92</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,98; 10,99</t>
+          <t>6,75; 11,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,24; 10,94</t>
+          <t>7,25; 11,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,63; 10,34</t>
+          <t>7,56; 10,33</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2608</t>
+          <t>0; 2882</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2684</t>
+          <t>0; 2590</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>995; 9238</t>
+          <t>1128; 8290</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3415; 12168</t>
+          <t>3423; 12384</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6267; 17450</t>
+          <t>6222; 17242</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>542; 6093</t>
+          <t>538; 5654</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>770; 7061</t>
+          <t>758; 7532</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2514; 10801</t>
+          <t>2209; 9934</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2547; 10763</t>
+          <t>2432; 10563</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 8801</t>
+          <t>0; 8072</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3952; 14910</t>
+          <t>3536; 15092</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2084</t>
+          <t>0; 1820</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 7975</t>
+          <t>0; 8920</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>375; 10173</t>
+          <t>377; 8000</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1430; 7455</t>
+          <t>1396; 7469</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>955; 6067</t>
+          <t>1079; 5440</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3358; 10861</t>
+          <t>3399; 10637</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4490; 13840</t>
+          <t>4463; 14142</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2373; 12339</t>
+          <t>2507; 11741</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9136; 22323</t>
+          <t>9096; 21982</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>25907; 43505</t>
+          <t>26183; 42651</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>33995; 53564</t>
+          <t>33365; 53706</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>65234; 92325</t>
+          <t>63428; 90402</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>45492; 71648</t>
+          <t>43995; 71708</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>53846; 81387</t>
+          <t>53950; 82476</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>106580; 144431</t>
+          <t>105592; 144159</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$recibos_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$recibos_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,72</t>
+          <t>0,0; 1,94</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 6,58</t>
+          <t>2,42; 8,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,7; 9,78</t>
+          <t>1,52; 8,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,46; 6,83</t>
+          <t>2,75; 7,4</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 10,12</t>
+          <t>1,08; 10,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 11,45</t>
+          <t>0,88; 9,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,82; 8,17</t>
+          <t>1,82; 8,54</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,62; 15,7</t>
+          <t>0,0; 14,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,96</t>
+          <t>4,08; 18,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 10,71</t>
+          <t>2,65; 11,04</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,27</t>
+          <t>0,0; 10,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,18</t>
+          <t>0,0; 9,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 10,71</t>
+          <t>0,63; 6,53</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,07; 16,42</t>
+          <t>1,67; 9,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,94; 9,78</t>
+          <t>2,78; 15,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,36; 10,52</t>
+          <t>3,3; 10,82</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,73; 11,82</t>
+          <t>1,65; 8,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,65; 7,74</t>
+          <t>3,74; 11,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,35; 8,1</t>
+          <t>3,61; 8,7</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>26,67%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>20,02; 32,62</t>
+          <t>22,52; 35,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21,88; 35,22</t>
+          <t>18,83; 31,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22,39; 31,92</t>
+          <t>22,0; 31,38</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,75; 11,0</t>
+          <t>7,62; 11,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,25; 11,08</t>
+          <t>7,88; 12,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,56; 10,33</t>
+          <t>8,1; 10,99</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>455</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>455</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2882</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2491</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2590</t>
+          <t>0; 2308</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>5628</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6796</t>
+          <t>4245</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10647</t>
+          <t>9872</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1128; 8290</t>
+          <t>2782; 9881</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3423; 12384</t>
+          <t>1521; 8659</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6222; 17242</t>
+          <t>5905; 15896</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2157</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2972</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>4612</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>538; 5654</t>
+          <t>626; 6326</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>758; 7532</t>
+          <t>476; 5191</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2209; 9934</t>
+          <t>2043; 9597</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>5610</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>5860</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7978</t>
+          <t>8327</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2432; 10563</t>
+          <t>0; 9570</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 8072</t>
+          <t>2791; 12578</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3536; 15092</t>
+          <t>3584; 14945</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>478</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>1780</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1820</t>
+          <t>0; 4168</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 8920</t>
+          <t>0; 3349</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>377; 8000</t>
+          <t>473; 4878</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>3616</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6234</t>
+          <t>5529</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1396; 7469</t>
+          <t>808; 4782</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1079; 5440</t>
+          <t>1255; 6885</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3399; 10637</t>
+          <t>3085; 10120</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>8363</t>
+          <t>5922</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14280</t>
+          <t>14444</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4463; 14142</t>
+          <t>2267; 12017</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2507; 11741</t>
+          <t>4432; 14113</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9096; 21982</t>
+          <t>9219; 22235</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>51</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>33636</t>
+          <t>44131</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>43340</t>
+          <t>34525</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>76976</t>
+          <t>78656</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>26183; 42651</t>
+          <t>34990; 55720</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>33365; 53706</t>
+          <t>26286; 44024</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>63428; 90402</t>
+          <t>64904; 92567</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>89</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>58120</t>
+          <t>64371</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>66273</t>
+          <t>59305</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>124393</t>
+          <t>123676</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>43995; 71708</t>
+          <t>52080; 79556</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>53950; 82476</t>
+          <t>48592; 74042</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>105592; 144159</t>
+          <t>105345; 142901</t>
         </is>
       </c>
     </row>
